--- a/assets/Abra_Zylo_Customer_Import_Template.xlsx
+++ b/assets/Abra_Zylo_Customer_Import_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customers'!$A$1:$D$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customers'!$A$1:$C$501</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,25 +31,16 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -57,22 +48,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00808080"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,13 +424,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D501"/>
+  <dimension ref="A1:C501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,11 +445,6 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Security Code</t>
         </is>
       </c>
@@ -472,8 +452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -482,8 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -492,8 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -502,8 +479,7 @@
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -512,8 +488,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -522,8 +497,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -532,8 +506,7 @@
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -542,8 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -552,8 +524,7 @@
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -562,8 +533,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -572,8 +542,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -582,8 +551,7 @@
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -592,8 +560,7 @@
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -602,8 +569,7 @@
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -612,8 +578,7 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -622,8 +587,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -632,8 +596,7 @@
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -642,8 +605,7 @@
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -652,8 +614,7 @@
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -662,8 +623,7 @@
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -672,8 +632,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -682,8 +641,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -692,8 +650,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -702,8 +659,7 @@
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -712,8 +668,7 @@
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -722,8 +677,7 @@
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -732,8 +686,7 @@
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -742,8 +695,7 @@
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -752,8 +704,7 @@
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -762,8 +713,7 @@
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -772,8 +722,7 @@
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -782,8 +731,7 @@
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -792,8 +740,7 @@
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -802,8 +749,7 @@
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -812,8 +758,7 @@
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -822,8 +767,7 @@
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -832,8 +776,7 @@
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -842,8 +785,7 @@
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -852,8 +794,7 @@
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -862,8 +803,7 @@
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -872,8 +812,7 @@
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -882,8 +821,7 @@
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -892,8 +830,7 @@
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -902,8 +839,7 @@
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -912,8 +848,7 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -922,8 +857,7 @@
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -932,8 +866,7 @@
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -942,8 +875,7 @@
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -952,8 +884,7 @@
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -962,8 +893,7 @@
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -972,8 +902,7 @@
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -982,8 +911,7 @@
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -992,8 +920,7 @@
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1002,8 +929,7 @@
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1012,8 +938,7 @@
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1022,8 +947,7 @@
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1032,8 +956,7 @@
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1042,8 +965,7 @@
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1052,8 +974,7 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1062,8 +983,7 @@
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1072,8 +992,7 @@
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1082,8 +1001,7 @@
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1092,8 +1010,7 @@
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1102,8 +1019,7 @@
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1112,8 +1028,7 @@
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1122,8 +1037,7 @@
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1132,8 +1046,7 @@
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1142,8 +1055,7 @@
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1152,8 +1064,7 @@
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1162,8 +1073,7 @@
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1172,8 +1082,7 @@
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1182,8 +1091,7 @@
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1192,8 +1100,7 @@
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1202,8 +1109,7 @@
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1212,8 +1118,7 @@
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1222,8 +1127,7 @@
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1232,8 +1136,7 @@
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1242,8 +1145,7 @@
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1252,8 +1154,7 @@
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1262,8 +1163,7 @@
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1272,8 +1172,7 @@
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1282,8 +1181,7 @@
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1292,8 +1190,7 @@
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1302,8 +1199,7 @@
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1312,8 +1208,7 @@
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1322,8 +1217,7 @@
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1332,8 +1226,7 @@
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1342,8 +1235,7 @@
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1352,8 +1244,7 @@
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1362,8 +1253,7 @@
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1372,8 +1262,7 @@
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1382,8 +1271,7 @@
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1392,8 +1280,7 @@
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1402,8 +1289,7 @@
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1412,8 +1298,7 @@
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1422,8 +1307,7 @@
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" s="2" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1432,8 +1316,7 @@
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1442,8 +1325,7 @@
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1452,8 +1334,7 @@
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1462,8 +1343,7 @@
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1472,8 +1352,7 @@
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1482,8 +1361,7 @@
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" s="2" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1492,8 +1370,7 @@
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1502,8 +1379,7 @@
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1512,8 +1388,7 @@
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" s="2" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1522,8 +1397,7 @@
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1532,8 +1406,7 @@
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" s="2" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1542,8 +1415,7 @@
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" s="2" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1552,8 +1424,7 @@
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" s="2" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1562,8 +1433,7 @@
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" s="2" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1572,8 +1442,7 @@
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" s="2" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1582,8 +1451,7 @@
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" s="2" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1592,8 +1460,7 @@
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" s="2" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1602,8 +1469,7 @@
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" s="2" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1612,8 +1478,7 @@
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" s="2" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1622,8 +1487,7 @@
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" s="2" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1632,8 +1496,7 @@
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" s="2" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1642,8 +1505,7 @@
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" s="2" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1652,8 +1514,7 @@
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" s="2" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1662,8 +1523,7 @@
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" s="2" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1672,8 +1532,7 @@
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" s="2" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1682,8 +1541,7 @@
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" s="2" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1692,8 +1550,7 @@
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" s="2" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1702,8 +1559,7 @@
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" s="2" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1712,8 +1568,7 @@
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" s="2" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1722,8 +1577,7 @@
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" s="2" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1732,8 +1586,7 @@
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" s="2" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1742,8 +1595,7 @@
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" s="2" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1752,8 +1604,7 @@
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" s="2" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1762,8 +1613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" s="2" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1772,8 +1622,7 @@
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" s="2" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1782,8 +1631,7 @@
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" s="2" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1792,8 +1640,7 @@
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" s="2" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1802,8 +1649,7 @@
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" s="2" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1812,8 +1658,7 @@
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" s="2" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1822,8 +1667,7 @@
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" s="2" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1832,8 +1676,7 @@
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" s="2" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1842,8 +1685,7 @@
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" s="2" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1852,8 +1694,7 @@
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" s="2" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1862,8 +1703,7 @@
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" s="2" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1872,8 +1712,7 @@
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" s="2" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1882,8 +1721,7 @@
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" s="2" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1892,8 +1730,7 @@
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" s="2" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1902,8 +1739,7 @@
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" s="2" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1912,8 +1748,7 @@
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" s="2" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1922,8 +1757,7 @@
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" s="2" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1932,8 +1766,7 @@
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" s="2" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1942,8 +1775,7 @@
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" s="2" t="inlineStr"/>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1952,8 +1784,7 @@
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" s="2" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1962,8 +1793,7 @@
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" s="2" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1972,8 +1802,7 @@
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" s="2" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1982,8 +1811,7 @@
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" s="2" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -1992,8 +1820,7 @@
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" s="2" t="inlineStr"/>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2002,8 +1829,7 @@
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" s="2" t="inlineStr"/>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2012,8 +1838,7 @@
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" s="2" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2022,8 +1847,7 @@
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" s="2" t="inlineStr"/>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2032,8 +1856,7 @@
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" s="2" t="inlineStr"/>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2042,8 +1865,7 @@
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" s="2" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2052,8 +1874,7 @@
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" s="2" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2062,8 +1883,7 @@
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" s="2" t="inlineStr"/>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2072,8 +1892,7 @@
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" s="2" t="inlineStr"/>
-      <c r="C162" t="inlineStr"/>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2082,8 +1901,7 @@
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" s="2" t="inlineStr"/>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2092,8 +1910,7 @@
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" s="2" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2102,8 +1919,7 @@
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" s="2" t="inlineStr"/>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2112,8 +1928,7 @@
     <row r="166">
       <c r="A166" t="inlineStr"/>
       <c r="B166" s="2" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2122,8 +1937,7 @@
     <row r="167">
       <c r="A167" t="inlineStr"/>
       <c r="B167" s="2" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2132,8 +1946,7 @@
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" s="2" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2142,8 +1955,7 @@
     <row r="169">
       <c r="A169" t="inlineStr"/>
       <c r="B169" s="2" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2152,8 +1964,7 @@
     <row r="170">
       <c r="A170" t="inlineStr"/>
       <c r="B170" s="2" t="inlineStr"/>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2162,8 +1973,7 @@
     <row r="171">
       <c r="A171" t="inlineStr"/>
       <c r="B171" s="2" t="inlineStr"/>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2172,8 +1982,7 @@
     <row r="172">
       <c r="A172" t="inlineStr"/>
       <c r="B172" s="2" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2182,8 +1991,7 @@
     <row r="173">
       <c r="A173" t="inlineStr"/>
       <c r="B173" s="2" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2192,8 +2000,7 @@
     <row r="174">
       <c r="A174" t="inlineStr"/>
       <c r="B174" s="2" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2202,8 +2009,7 @@
     <row r="175">
       <c r="A175" t="inlineStr"/>
       <c r="B175" s="2" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2212,8 +2018,7 @@
     <row r="176">
       <c r="A176" t="inlineStr"/>
       <c r="B176" s="2" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2222,8 +2027,7 @@
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" s="2" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2232,8 +2036,7 @@
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" s="2" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2242,8 +2045,7 @@
     <row r="179">
       <c r="A179" t="inlineStr"/>
       <c r="B179" s="2" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2252,8 +2054,7 @@
     <row r="180">
       <c r="A180" t="inlineStr"/>
       <c r="B180" s="2" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2262,8 +2063,7 @@
     <row r="181">
       <c r="A181" t="inlineStr"/>
       <c r="B181" s="2" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2272,8 +2072,7 @@
     <row r="182">
       <c r="A182" t="inlineStr"/>
       <c r="B182" s="2" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2282,8 +2081,7 @@
     <row r="183">
       <c r="A183" t="inlineStr"/>
       <c r="B183" s="2" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2292,8 +2090,7 @@
     <row r="184">
       <c r="A184" t="inlineStr"/>
       <c r="B184" s="2" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2302,8 +2099,7 @@
     <row r="185">
       <c r="A185" t="inlineStr"/>
       <c r="B185" s="2" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2312,8 +2108,7 @@
     <row r="186">
       <c r="A186" t="inlineStr"/>
       <c r="B186" s="2" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2322,8 +2117,7 @@
     <row r="187">
       <c r="A187" t="inlineStr"/>
       <c r="B187" s="2" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2332,8 +2126,7 @@
     <row r="188">
       <c r="A188" t="inlineStr"/>
       <c r="B188" s="2" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2342,8 +2135,7 @@
     <row r="189">
       <c r="A189" t="inlineStr"/>
       <c r="B189" s="2" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2352,8 +2144,7 @@
     <row r="190">
       <c r="A190" t="inlineStr"/>
       <c r="B190" s="2" t="inlineStr"/>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2362,8 +2153,7 @@
     <row r="191">
       <c r="A191" t="inlineStr"/>
       <c r="B191" s="2" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2372,8 +2162,7 @@
     <row r="192">
       <c r="A192" t="inlineStr"/>
       <c r="B192" s="2" t="inlineStr"/>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2382,8 +2171,7 @@
     <row r="193">
       <c r="A193" t="inlineStr"/>
       <c r="B193" s="2" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2392,8 +2180,7 @@
     <row r="194">
       <c r="A194" t="inlineStr"/>
       <c r="B194" s="2" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2402,8 +2189,7 @@
     <row r="195">
       <c r="A195" t="inlineStr"/>
       <c r="B195" s="2" t="inlineStr"/>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2412,8 +2198,7 @@
     <row r="196">
       <c r="A196" t="inlineStr"/>
       <c r="B196" s="2" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2422,8 +2207,7 @@
     <row r="197">
       <c r="A197" t="inlineStr"/>
       <c r="B197" s="2" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2432,8 +2216,7 @@
     <row r="198">
       <c r="A198" t="inlineStr"/>
       <c r="B198" s="2" t="inlineStr"/>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2442,8 +2225,7 @@
     <row r="199">
       <c r="A199" t="inlineStr"/>
       <c r="B199" s="2" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2452,8 +2234,7 @@
     <row r="200">
       <c r="A200" t="inlineStr"/>
       <c r="B200" s="2" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2462,8 +2243,7 @@
     <row r="201">
       <c r="A201" t="inlineStr"/>
       <c r="B201" s="2" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2472,8 +2252,7 @@
     <row r="202">
       <c r="A202" t="inlineStr"/>
       <c r="B202" s="2" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2482,8 +2261,7 @@
     <row r="203">
       <c r="A203" t="inlineStr"/>
       <c r="B203" s="2" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2492,8 +2270,7 @@
     <row r="204">
       <c r="A204" t="inlineStr"/>
       <c r="B204" s="2" t="inlineStr"/>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2502,8 +2279,7 @@
     <row r="205">
       <c r="A205" t="inlineStr"/>
       <c r="B205" s="2" t="inlineStr"/>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2512,8 +2288,7 @@
     <row r="206">
       <c r="A206" t="inlineStr"/>
       <c r="B206" s="2" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2522,8 +2297,7 @@
     <row r="207">
       <c r="A207" t="inlineStr"/>
       <c r="B207" s="2" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2532,8 +2306,7 @@
     <row r="208">
       <c r="A208" t="inlineStr"/>
       <c r="B208" s="2" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2542,8 +2315,7 @@
     <row r="209">
       <c r="A209" t="inlineStr"/>
       <c r="B209" s="2" t="inlineStr"/>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2552,8 +2324,7 @@
     <row r="210">
       <c r="A210" t="inlineStr"/>
       <c r="B210" s="2" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2562,8 +2333,7 @@
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" s="2" t="inlineStr"/>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2572,8 +2342,7 @@
     <row r="212">
       <c r="A212" t="inlineStr"/>
       <c r="B212" s="2" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2582,8 +2351,7 @@
     <row r="213">
       <c r="A213" t="inlineStr"/>
       <c r="B213" s="2" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2592,8 +2360,7 @@
     <row r="214">
       <c r="A214" t="inlineStr"/>
       <c r="B214" s="2" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2602,8 +2369,7 @@
     <row r="215">
       <c r="A215" t="inlineStr"/>
       <c r="B215" s="2" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="C215" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2612,8 +2378,7 @@
     <row r="216">
       <c r="A216" t="inlineStr"/>
       <c r="B216" s="2" t="inlineStr"/>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2622,8 +2387,7 @@
     <row r="217">
       <c r="A217" t="inlineStr"/>
       <c r="B217" s="2" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2632,8 +2396,7 @@
     <row r="218">
       <c r="A218" t="inlineStr"/>
       <c r="B218" s="2" t="inlineStr"/>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2642,8 +2405,7 @@
     <row r="219">
       <c r="A219" t="inlineStr"/>
       <c r="B219" s="2" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2652,8 +2414,7 @@
     <row r="220">
       <c r="A220" t="inlineStr"/>
       <c r="B220" s="2" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2662,8 +2423,7 @@
     <row r="221">
       <c r="A221" t="inlineStr"/>
       <c r="B221" s="2" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2672,8 +2432,7 @@
     <row r="222">
       <c r="A222" t="inlineStr"/>
       <c r="B222" s="2" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2682,8 +2441,7 @@
     <row r="223">
       <c r="A223" t="inlineStr"/>
       <c r="B223" s="2" t="inlineStr"/>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2692,8 +2450,7 @@
     <row r="224">
       <c r="A224" t="inlineStr"/>
       <c r="B224" s="2" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2702,8 +2459,7 @@
     <row r="225">
       <c r="A225" t="inlineStr"/>
       <c r="B225" s="2" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2712,8 +2468,7 @@
     <row r="226">
       <c r="A226" t="inlineStr"/>
       <c r="B226" s="2" t="inlineStr"/>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2722,8 +2477,7 @@
     <row r="227">
       <c r="A227" t="inlineStr"/>
       <c r="B227" s="2" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2732,8 +2486,7 @@
     <row r="228">
       <c r="A228" t="inlineStr"/>
       <c r="B228" s="2" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2742,8 +2495,7 @@
     <row r="229">
       <c r="A229" t="inlineStr"/>
       <c r="B229" s="2" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2752,8 +2504,7 @@
     <row r="230">
       <c r="A230" t="inlineStr"/>
       <c r="B230" s="2" t="inlineStr"/>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2762,8 +2513,7 @@
     <row r="231">
       <c r="A231" t="inlineStr"/>
       <c r="B231" s="2" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="C231" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2772,8 +2522,7 @@
     <row r="232">
       <c r="A232" t="inlineStr"/>
       <c r="B232" s="2" t="inlineStr"/>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2782,8 +2531,7 @@
     <row r="233">
       <c r="A233" t="inlineStr"/>
       <c r="B233" s="2" t="inlineStr"/>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2792,8 +2540,7 @@
     <row r="234">
       <c r="A234" t="inlineStr"/>
       <c r="B234" s="2" t="inlineStr"/>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2802,8 +2549,7 @@
     <row r="235">
       <c r="A235" t="inlineStr"/>
       <c r="B235" s="2" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2812,8 +2558,7 @@
     <row r="236">
       <c r="A236" t="inlineStr"/>
       <c r="B236" s="2" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="C236" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2822,8 +2567,7 @@
     <row r="237">
       <c r="A237" t="inlineStr"/>
       <c r="B237" s="2" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2832,8 +2576,7 @@
     <row r="238">
       <c r="A238" t="inlineStr"/>
       <c r="B238" s="2" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2842,8 +2585,7 @@
     <row r="239">
       <c r="A239" t="inlineStr"/>
       <c r="B239" s="2" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2852,8 +2594,7 @@
     <row r="240">
       <c r="A240" t="inlineStr"/>
       <c r="B240" s="2" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2862,8 +2603,7 @@
     <row r="241">
       <c r="A241" t="inlineStr"/>
       <c r="B241" s="2" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2872,8 +2612,7 @@
     <row r="242">
       <c r="A242" t="inlineStr"/>
       <c r="B242" s="2" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2882,8 +2621,7 @@
     <row r="243">
       <c r="A243" t="inlineStr"/>
       <c r="B243" s="2" t="inlineStr"/>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2892,8 +2630,7 @@
     <row r="244">
       <c r="A244" t="inlineStr"/>
       <c r="B244" s="2" t="inlineStr"/>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2902,8 +2639,7 @@
     <row r="245">
       <c r="A245" t="inlineStr"/>
       <c r="B245" s="2" t="inlineStr"/>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2912,8 +2648,7 @@
     <row r="246">
       <c r="A246" t="inlineStr"/>
       <c r="B246" s="2" t="inlineStr"/>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2922,8 +2657,7 @@
     <row r="247">
       <c r="A247" t="inlineStr"/>
       <c r="B247" s="2" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="C247" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2932,8 +2666,7 @@
     <row r="248">
       <c r="A248" t="inlineStr"/>
       <c r="B248" s="2" t="inlineStr"/>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2942,8 +2675,7 @@
     <row r="249">
       <c r="A249" t="inlineStr"/>
       <c r="B249" s="2" t="inlineStr"/>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2952,8 +2684,7 @@
     <row r="250">
       <c r="A250" t="inlineStr"/>
       <c r="B250" s="2" t="inlineStr"/>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2962,8 +2693,7 @@
     <row r="251">
       <c r="A251" t="inlineStr"/>
       <c r="B251" s="2" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2972,8 +2702,7 @@
     <row r="252">
       <c r="A252" t="inlineStr"/>
       <c r="B252" s="2" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2982,8 +2711,7 @@
     <row r="253">
       <c r="A253" t="inlineStr"/>
       <c r="B253" s="2" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -2992,8 +2720,7 @@
     <row r="254">
       <c r="A254" t="inlineStr"/>
       <c r="B254" s="2" t="inlineStr"/>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3002,8 +2729,7 @@
     <row r="255">
       <c r="A255" t="inlineStr"/>
       <c r="B255" s="2" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3012,8 +2738,7 @@
     <row r="256">
       <c r="A256" t="inlineStr"/>
       <c r="B256" s="2" t="inlineStr"/>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3022,8 +2747,7 @@
     <row r="257">
       <c r="A257" t="inlineStr"/>
       <c r="B257" s="2" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3032,8 +2756,7 @@
     <row r="258">
       <c r="A258" t="inlineStr"/>
       <c r="B258" s="2" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3042,8 +2765,7 @@
     <row r="259">
       <c r="A259" t="inlineStr"/>
       <c r="B259" s="2" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3052,8 +2774,7 @@
     <row r="260">
       <c r="A260" t="inlineStr"/>
       <c r="B260" s="2" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3062,8 +2783,7 @@
     <row r="261">
       <c r="A261" t="inlineStr"/>
       <c r="B261" s="2" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3072,8 +2792,7 @@
     <row r="262">
       <c r="A262" t="inlineStr"/>
       <c r="B262" s="2" t="inlineStr"/>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3082,8 +2801,7 @@
     <row r="263">
       <c r="A263" t="inlineStr"/>
       <c r="B263" s="2" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3092,8 +2810,7 @@
     <row r="264">
       <c r="A264" t="inlineStr"/>
       <c r="B264" s="2" t="inlineStr"/>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3102,8 +2819,7 @@
     <row r="265">
       <c r="A265" t="inlineStr"/>
       <c r="B265" s="2" t="inlineStr"/>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3112,8 +2828,7 @@
     <row r="266">
       <c r="A266" t="inlineStr"/>
       <c r="B266" s="2" t="inlineStr"/>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="C266" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3122,8 +2837,7 @@
     <row r="267">
       <c r="A267" t="inlineStr"/>
       <c r="B267" s="2" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="C267" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3132,8 +2846,7 @@
     <row r="268">
       <c r="A268" t="inlineStr"/>
       <c r="B268" s="2" t="inlineStr"/>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3142,8 +2855,7 @@
     <row r="269">
       <c r="A269" t="inlineStr"/>
       <c r="B269" s="2" t="inlineStr"/>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="C269" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3152,8 +2864,7 @@
     <row r="270">
       <c r="A270" t="inlineStr"/>
       <c r="B270" s="2" t="inlineStr"/>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="C270" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3162,8 +2873,7 @@
     <row r="271">
       <c r="A271" t="inlineStr"/>
       <c r="B271" s="2" t="inlineStr"/>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="C271" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3172,8 +2882,7 @@
     <row r="272">
       <c r="A272" t="inlineStr"/>
       <c r="B272" s="2" t="inlineStr"/>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="C272" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3182,8 +2891,7 @@
     <row r="273">
       <c r="A273" t="inlineStr"/>
       <c r="B273" s="2" t="inlineStr"/>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3192,8 +2900,7 @@
     <row r="274">
       <c r="A274" t="inlineStr"/>
       <c r="B274" s="2" t="inlineStr"/>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3202,8 +2909,7 @@
     <row r="275">
       <c r="A275" t="inlineStr"/>
       <c r="B275" s="2" t="inlineStr"/>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="C275" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3212,8 +2918,7 @@
     <row r="276">
       <c r="A276" t="inlineStr"/>
       <c r="B276" s="2" t="inlineStr"/>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3222,8 +2927,7 @@
     <row r="277">
       <c r="A277" t="inlineStr"/>
       <c r="B277" s="2" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3232,8 +2936,7 @@
     <row r="278">
       <c r="A278" t="inlineStr"/>
       <c r="B278" s="2" t="inlineStr"/>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3242,8 +2945,7 @@
     <row r="279">
       <c r="A279" t="inlineStr"/>
       <c r="B279" s="2" t="inlineStr"/>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3252,8 +2954,7 @@
     <row r="280">
       <c r="A280" t="inlineStr"/>
       <c r="B280" s="2" t="inlineStr"/>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3262,8 +2963,7 @@
     <row r="281">
       <c r="A281" t="inlineStr"/>
       <c r="B281" s="2" t="inlineStr"/>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3272,8 +2972,7 @@
     <row r="282">
       <c r="A282" t="inlineStr"/>
       <c r="B282" s="2" t="inlineStr"/>
-      <c r="C282" t="inlineStr"/>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3282,8 +2981,7 @@
     <row r="283">
       <c r="A283" t="inlineStr"/>
       <c r="B283" s="2" t="inlineStr"/>
-      <c r="C283" t="inlineStr"/>
-      <c r="D283" s="2" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3292,8 +2990,7 @@
     <row r="284">
       <c r="A284" t="inlineStr"/>
       <c r="B284" s="2" t="inlineStr"/>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3302,8 +2999,7 @@
     <row r="285">
       <c r="A285" t="inlineStr"/>
       <c r="B285" s="2" t="inlineStr"/>
-      <c r="C285" t="inlineStr"/>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="C285" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3312,8 +3008,7 @@
     <row r="286">
       <c r="A286" t="inlineStr"/>
       <c r="B286" s="2" t="inlineStr"/>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3322,8 +3017,7 @@
     <row r="287">
       <c r="A287" t="inlineStr"/>
       <c r="B287" s="2" t="inlineStr"/>
-      <c r="C287" t="inlineStr"/>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3332,8 +3026,7 @@
     <row r="288">
       <c r="A288" t="inlineStr"/>
       <c r="B288" s="2" t="inlineStr"/>
-      <c r="C288" t="inlineStr"/>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3342,8 +3035,7 @@
     <row r="289">
       <c r="A289" t="inlineStr"/>
       <c r="B289" s="2" t="inlineStr"/>
-      <c r="C289" t="inlineStr"/>
-      <c r="D289" s="2" t="inlineStr">
+      <c r="C289" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3352,8 +3044,7 @@
     <row r="290">
       <c r="A290" t="inlineStr"/>
       <c r="B290" s="2" t="inlineStr"/>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" s="2" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3362,8 +3053,7 @@
     <row r="291">
       <c r="A291" t="inlineStr"/>
       <c r="B291" s="2" t="inlineStr"/>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" s="2" t="inlineStr">
+      <c r="C291" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3372,8 +3062,7 @@
     <row r="292">
       <c r="A292" t="inlineStr"/>
       <c r="B292" s="2" t="inlineStr"/>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" s="2" t="inlineStr">
+      <c r="C292" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3382,8 +3071,7 @@
     <row r="293">
       <c r="A293" t="inlineStr"/>
       <c r="B293" s="2" t="inlineStr"/>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" s="2" t="inlineStr">
+      <c r="C293" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3392,8 +3080,7 @@
     <row r="294">
       <c r="A294" t="inlineStr"/>
       <c r="B294" s="2" t="inlineStr"/>
-      <c r="C294" t="inlineStr"/>
-      <c r="D294" s="2" t="inlineStr">
+      <c r="C294" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3402,8 +3089,7 @@
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" s="2" t="inlineStr"/>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" s="2" t="inlineStr">
+      <c r="C295" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3412,8 +3098,7 @@
     <row r="296">
       <c r="A296" t="inlineStr"/>
       <c r="B296" s="2" t="inlineStr"/>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" s="2" t="inlineStr">
+      <c r="C296" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3422,8 +3107,7 @@
     <row r="297">
       <c r="A297" t="inlineStr"/>
       <c r="B297" s="2" t="inlineStr"/>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" s="2" t="inlineStr">
+      <c r="C297" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3432,8 +3116,7 @@
     <row r="298">
       <c r="A298" t="inlineStr"/>
       <c r="B298" s="2" t="inlineStr"/>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" s="2" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3442,8 +3125,7 @@
     <row r="299">
       <c r="A299" t="inlineStr"/>
       <c r="B299" s="2" t="inlineStr"/>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" s="2" t="inlineStr">
+      <c r="C299" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3452,8 +3134,7 @@
     <row r="300">
       <c r="A300" t="inlineStr"/>
       <c r="B300" s="2" t="inlineStr"/>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="C300" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3462,8 +3143,7 @@
     <row r="301">
       <c r="A301" t="inlineStr"/>
       <c r="B301" s="2" t="inlineStr"/>
-      <c r="C301" t="inlineStr"/>
-      <c r="D301" s="2" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3472,8 +3152,7 @@
     <row r="302">
       <c r="A302" t="inlineStr"/>
       <c r="B302" s="2" t="inlineStr"/>
-      <c r="C302" t="inlineStr"/>
-      <c r="D302" s="2" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3482,8 +3161,7 @@
     <row r="303">
       <c r="A303" t="inlineStr"/>
       <c r="B303" s="2" t="inlineStr"/>
-      <c r="C303" t="inlineStr"/>
-      <c r="D303" s="2" t="inlineStr">
+      <c r="C303" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3492,8 +3170,7 @@
     <row r="304">
       <c r="A304" t="inlineStr"/>
       <c r="B304" s="2" t="inlineStr"/>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" s="2" t="inlineStr">
+      <c r="C304" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3502,8 +3179,7 @@
     <row r="305">
       <c r="A305" t="inlineStr"/>
       <c r="B305" s="2" t="inlineStr"/>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" s="2" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3512,8 +3188,7 @@
     <row r="306">
       <c r="A306" t="inlineStr"/>
       <c r="B306" s="2" t="inlineStr"/>
-      <c r="C306" t="inlineStr"/>
-      <c r="D306" s="2" t="inlineStr">
+      <c r="C306" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3522,8 +3197,7 @@
     <row r="307">
       <c r="A307" t="inlineStr"/>
       <c r="B307" s="2" t="inlineStr"/>
-      <c r="C307" t="inlineStr"/>
-      <c r="D307" s="2" t="inlineStr">
+      <c r="C307" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3532,8 +3206,7 @@
     <row r="308">
       <c r="A308" t="inlineStr"/>
       <c r="B308" s="2" t="inlineStr"/>
-      <c r="C308" t="inlineStr"/>
-      <c r="D308" s="2" t="inlineStr">
+      <c r="C308" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3542,8 +3215,7 @@
     <row r="309">
       <c r="A309" t="inlineStr"/>
       <c r="B309" s="2" t="inlineStr"/>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" s="2" t="inlineStr">
+      <c r="C309" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3552,8 +3224,7 @@
     <row r="310">
       <c r="A310" t="inlineStr"/>
       <c r="B310" s="2" t="inlineStr"/>
-      <c r="C310" t="inlineStr"/>
-      <c r="D310" s="2" t="inlineStr">
+      <c r="C310" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3562,8 +3233,7 @@
     <row r="311">
       <c r="A311" t="inlineStr"/>
       <c r="B311" s="2" t="inlineStr"/>
-      <c r="C311" t="inlineStr"/>
-      <c r="D311" s="2" t="inlineStr">
+      <c r="C311" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3572,8 +3242,7 @@
     <row r="312">
       <c r="A312" t="inlineStr"/>
       <c r="B312" s="2" t="inlineStr"/>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" s="2" t="inlineStr">
+      <c r="C312" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3582,8 +3251,7 @@
     <row r="313">
       <c r="A313" t="inlineStr"/>
       <c r="B313" s="2" t="inlineStr"/>
-      <c r="C313" t="inlineStr"/>
-      <c r="D313" s="2" t="inlineStr">
+      <c r="C313" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3592,8 +3260,7 @@
     <row r="314">
       <c r="A314" t="inlineStr"/>
       <c r="B314" s="2" t="inlineStr"/>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" s="2" t="inlineStr">
+      <c r="C314" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3602,8 +3269,7 @@
     <row r="315">
       <c r="A315" t="inlineStr"/>
       <c r="B315" s="2" t="inlineStr"/>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" s="2" t="inlineStr">
+      <c r="C315" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3612,8 +3278,7 @@
     <row r="316">
       <c r="A316" t="inlineStr"/>
       <c r="B316" s="2" t="inlineStr"/>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" s="2" t="inlineStr">
+      <c r="C316" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3622,8 +3287,7 @@
     <row r="317">
       <c r="A317" t="inlineStr"/>
       <c r="B317" s="2" t="inlineStr"/>
-      <c r="C317" t="inlineStr"/>
-      <c r="D317" s="2" t="inlineStr">
+      <c r="C317" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3632,8 +3296,7 @@
     <row r="318">
       <c r="A318" t="inlineStr"/>
       <c r="B318" s="2" t="inlineStr"/>
-      <c r="C318" t="inlineStr"/>
-      <c r="D318" s="2" t="inlineStr">
+      <c r="C318" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3642,8 +3305,7 @@
     <row r="319">
       <c r="A319" t="inlineStr"/>
       <c r="B319" s="2" t="inlineStr"/>
-      <c r="C319" t="inlineStr"/>
-      <c r="D319" s="2" t="inlineStr">
+      <c r="C319" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3652,8 +3314,7 @@
     <row r="320">
       <c r="A320" t="inlineStr"/>
       <c r="B320" s="2" t="inlineStr"/>
-      <c r="C320" t="inlineStr"/>
-      <c r="D320" s="2" t="inlineStr">
+      <c r="C320" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3662,8 +3323,7 @@
     <row r="321">
       <c r="A321" t="inlineStr"/>
       <c r="B321" s="2" t="inlineStr"/>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" s="2" t="inlineStr">
+      <c r="C321" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3672,8 +3332,7 @@
     <row r="322">
       <c r="A322" t="inlineStr"/>
       <c r="B322" s="2" t="inlineStr"/>
-      <c r="C322" t="inlineStr"/>
-      <c r="D322" s="2" t="inlineStr">
+      <c r="C322" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3682,8 +3341,7 @@
     <row r="323">
       <c r="A323" t="inlineStr"/>
       <c r="B323" s="2" t="inlineStr"/>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" s="2" t="inlineStr">
+      <c r="C323" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3692,8 +3350,7 @@
     <row r="324">
       <c r="A324" t="inlineStr"/>
       <c r="B324" s="2" t="inlineStr"/>
-      <c r="C324" t="inlineStr"/>
-      <c r="D324" s="2" t="inlineStr">
+      <c r="C324" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3702,8 +3359,7 @@
     <row r="325">
       <c r="A325" t="inlineStr"/>
       <c r="B325" s="2" t="inlineStr"/>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" s="2" t="inlineStr">
+      <c r="C325" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3712,8 +3368,7 @@
     <row r="326">
       <c r="A326" t="inlineStr"/>
       <c r="B326" s="2" t="inlineStr"/>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" s="2" t="inlineStr">
+      <c r="C326" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3722,8 +3377,7 @@
     <row r="327">
       <c r="A327" t="inlineStr"/>
       <c r="B327" s="2" t="inlineStr"/>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" s="2" t="inlineStr">
+      <c r="C327" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3732,8 +3386,7 @@
     <row r="328">
       <c r="A328" t="inlineStr"/>
       <c r="B328" s="2" t="inlineStr"/>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" s="2" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3742,8 +3395,7 @@
     <row r="329">
       <c r="A329" t="inlineStr"/>
       <c r="B329" s="2" t="inlineStr"/>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" s="2" t="inlineStr">
+      <c r="C329" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3752,8 +3404,7 @@
     <row r="330">
       <c r="A330" t="inlineStr"/>
       <c r="B330" s="2" t="inlineStr"/>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" s="2" t="inlineStr">
+      <c r="C330" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3762,8 +3413,7 @@
     <row r="331">
       <c r="A331" t="inlineStr"/>
       <c r="B331" s="2" t="inlineStr"/>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" s="2" t="inlineStr">
+      <c r="C331" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3772,8 +3422,7 @@
     <row r="332">
       <c r="A332" t="inlineStr"/>
       <c r="B332" s="2" t="inlineStr"/>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" s="2" t="inlineStr">
+      <c r="C332" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3782,8 +3431,7 @@
     <row r="333">
       <c r="A333" t="inlineStr"/>
       <c r="B333" s="2" t="inlineStr"/>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" s="2" t="inlineStr">
+      <c r="C333" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3792,8 +3440,7 @@
     <row r="334">
       <c r="A334" t="inlineStr"/>
       <c r="B334" s="2" t="inlineStr"/>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" s="2" t="inlineStr">
+      <c r="C334" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3802,8 +3449,7 @@
     <row r="335">
       <c r="A335" t="inlineStr"/>
       <c r="B335" s="2" t="inlineStr"/>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" s="2" t="inlineStr">
+      <c r="C335" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3812,8 +3458,7 @@
     <row r="336">
       <c r="A336" t="inlineStr"/>
       <c r="B336" s="2" t="inlineStr"/>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" s="2" t="inlineStr">
+      <c r="C336" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3822,8 +3467,7 @@
     <row r="337">
       <c r="A337" t="inlineStr"/>
       <c r="B337" s="2" t="inlineStr"/>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" s="2" t="inlineStr">
+      <c r="C337" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3832,8 +3476,7 @@
     <row r="338">
       <c r="A338" t="inlineStr"/>
       <c r="B338" s="2" t="inlineStr"/>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" s="2" t="inlineStr">
+      <c r="C338" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3842,8 +3485,7 @@
     <row r="339">
       <c r="A339" t="inlineStr"/>
       <c r="B339" s="2" t="inlineStr"/>
-      <c r="C339" t="inlineStr"/>
-      <c r="D339" s="2" t="inlineStr">
+      <c r="C339" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3852,8 +3494,7 @@
     <row r="340">
       <c r="A340" t="inlineStr"/>
       <c r="B340" s="2" t="inlineStr"/>
-      <c r="C340" t="inlineStr"/>
-      <c r="D340" s="2" t="inlineStr">
+      <c r="C340" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3862,8 +3503,7 @@
     <row r="341">
       <c r="A341" t="inlineStr"/>
       <c r="B341" s="2" t="inlineStr"/>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" s="2" t="inlineStr">
+      <c r="C341" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3872,8 +3512,7 @@
     <row r="342">
       <c r="A342" t="inlineStr"/>
       <c r="B342" s="2" t="inlineStr"/>
-      <c r="C342" t="inlineStr"/>
-      <c r="D342" s="2" t="inlineStr">
+      <c r="C342" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3882,8 +3521,7 @@
     <row r="343">
       <c r="A343" t="inlineStr"/>
       <c r="B343" s="2" t="inlineStr"/>
-      <c r="C343" t="inlineStr"/>
-      <c r="D343" s="2" t="inlineStr">
+      <c r="C343" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3892,8 +3530,7 @@
     <row r="344">
       <c r="A344" t="inlineStr"/>
       <c r="B344" s="2" t="inlineStr"/>
-      <c r="C344" t="inlineStr"/>
-      <c r="D344" s="2" t="inlineStr">
+      <c r="C344" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3902,8 +3539,7 @@
     <row r="345">
       <c r="A345" t="inlineStr"/>
       <c r="B345" s="2" t="inlineStr"/>
-      <c r="C345" t="inlineStr"/>
-      <c r="D345" s="2" t="inlineStr">
+      <c r="C345" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3912,8 +3548,7 @@
     <row r="346">
       <c r="A346" t="inlineStr"/>
       <c r="B346" s="2" t="inlineStr"/>
-      <c r="C346" t="inlineStr"/>
-      <c r="D346" s="2" t="inlineStr">
+      <c r="C346" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3922,8 +3557,7 @@
     <row r="347">
       <c r="A347" t="inlineStr"/>
       <c r="B347" s="2" t="inlineStr"/>
-      <c r="C347" t="inlineStr"/>
-      <c r="D347" s="2" t="inlineStr">
+      <c r="C347" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3932,8 +3566,7 @@
     <row r="348">
       <c r="A348" t="inlineStr"/>
       <c r="B348" s="2" t="inlineStr"/>
-      <c r="C348" t="inlineStr"/>
-      <c r="D348" s="2" t="inlineStr">
+      <c r="C348" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3942,8 +3575,7 @@
     <row r="349">
       <c r="A349" t="inlineStr"/>
       <c r="B349" s="2" t="inlineStr"/>
-      <c r="C349" t="inlineStr"/>
-      <c r="D349" s="2" t="inlineStr">
+      <c r="C349" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3952,8 +3584,7 @@
     <row r="350">
       <c r="A350" t="inlineStr"/>
       <c r="B350" s="2" t="inlineStr"/>
-      <c r="C350" t="inlineStr"/>
-      <c r="D350" s="2" t="inlineStr">
+      <c r="C350" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3962,8 +3593,7 @@
     <row r="351">
       <c r="A351" t="inlineStr"/>
       <c r="B351" s="2" t="inlineStr"/>
-      <c r="C351" t="inlineStr"/>
-      <c r="D351" s="2" t="inlineStr">
+      <c r="C351" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3972,8 +3602,7 @@
     <row r="352">
       <c r="A352" t="inlineStr"/>
       <c r="B352" s="2" t="inlineStr"/>
-      <c r="C352" t="inlineStr"/>
-      <c r="D352" s="2" t="inlineStr">
+      <c r="C352" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3982,8 +3611,7 @@
     <row r="353">
       <c r="A353" t="inlineStr"/>
       <c r="B353" s="2" t="inlineStr"/>
-      <c r="C353" t="inlineStr"/>
-      <c r="D353" s="2" t="inlineStr">
+      <c r="C353" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -3992,8 +3620,7 @@
     <row r="354">
       <c r="A354" t="inlineStr"/>
       <c r="B354" s="2" t="inlineStr"/>
-      <c r="C354" t="inlineStr"/>
-      <c r="D354" s="2" t="inlineStr">
+      <c r="C354" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4002,8 +3629,7 @@
     <row r="355">
       <c r="A355" t="inlineStr"/>
       <c r="B355" s="2" t="inlineStr"/>
-      <c r="C355" t="inlineStr"/>
-      <c r="D355" s="2" t="inlineStr">
+      <c r="C355" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4012,8 +3638,7 @@
     <row r="356">
       <c r="A356" t="inlineStr"/>
       <c r="B356" s="2" t="inlineStr"/>
-      <c r="C356" t="inlineStr"/>
-      <c r="D356" s="2" t="inlineStr">
+      <c r="C356" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4022,8 +3647,7 @@
     <row r="357">
       <c r="A357" t="inlineStr"/>
       <c r="B357" s="2" t="inlineStr"/>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" s="2" t="inlineStr">
+      <c r="C357" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4032,8 +3656,7 @@
     <row r="358">
       <c r="A358" t="inlineStr"/>
       <c r="B358" s="2" t="inlineStr"/>
-      <c r="C358" t="inlineStr"/>
-      <c r="D358" s="2" t="inlineStr">
+      <c r="C358" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4042,8 +3665,7 @@
     <row r="359">
       <c r="A359" t="inlineStr"/>
       <c r="B359" s="2" t="inlineStr"/>
-      <c r="C359" t="inlineStr"/>
-      <c r="D359" s="2" t="inlineStr">
+      <c r="C359" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4052,8 +3674,7 @@
     <row r="360">
       <c r="A360" t="inlineStr"/>
       <c r="B360" s="2" t="inlineStr"/>
-      <c r="C360" t="inlineStr"/>
-      <c r="D360" s="2" t="inlineStr">
+      <c r="C360" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4062,8 +3683,7 @@
     <row r="361">
       <c r="A361" t="inlineStr"/>
       <c r="B361" s="2" t="inlineStr"/>
-      <c r="C361" t="inlineStr"/>
-      <c r="D361" s="2" t="inlineStr">
+      <c r="C361" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4072,8 +3692,7 @@
     <row r="362">
       <c r="A362" t="inlineStr"/>
       <c r="B362" s="2" t="inlineStr"/>
-      <c r="C362" t="inlineStr"/>
-      <c r="D362" s="2" t="inlineStr">
+      <c r="C362" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4082,8 +3701,7 @@
     <row r="363">
       <c r="A363" t="inlineStr"/>
       <c r="B363" s="2" t="inlineStr"/>
-      <c r="C363" t="inlineStr"/>
-      <c r="D363" s="2" t="inlineStr">
+      <c r="C363" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4092,8 +3710,7 @@
     <row r="364">
       <c r="A364" t="inlineStr"/>
       <c r="B364" s="2" t="inlineStr"/>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" s="2" t="inlineStr">
+      <c r="C364" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4102,8 +3719,7 @@
     <row r="365">
       <c r="A365" t="inlineStr"/>
       <c r="B365" s="2" t="inlineStr"/>
-      <c r="C365" t="inlineStr"/>
-      <c r="D365" s="2" t="inlineStr">
+      <c r="C365" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4112,8 +3728,7 @@
     <row r="366">
       <c r="A366" t="inlineStr"/>
       <c r="B366" s="2" t="inlineStr"/>
-      <c r="C366" t="inlineStr"/>
-      <c r="D366" s="2" t="inlineStr">
+      <c r="C366" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4122,8 +3737,7 @@
     <row r="367">
       <c r="A367" t="inlineStr"/>
       <c r="B367" s="2" t="inlineStr"/>
-      <c r="C367" t="inlineStr"/>
-      <c r="D367" s="2" t="inlineStr">
+      <c r="C367" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4132,8 +3746,7 @@
     <row r="368">
       <c r="A368" t="inlineStr"/>
       <c r="B368" s="2" t="inlineStr"/>
-      <c r="C368" t="inlineStr"/>
-      <c r="D368" s="2" t="inlineStr">
+      <c r="C368" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4142,8 +3755,7 @@
     <row r="369">
       <c r="A369" t="inlineStr"/>
       <c r="B369" s="2" t="inlineStr"/>
-      <c r="C369" t="inlineStr"/>
-      <c r="D369" s="2" t="inlineStr">
+      <c r="C369" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4152,8 +3764,7 @@
     <row r="370">
       <c r="A370" t="inlineStr"/>
       <c r="B370" s="2" t="inlineStr"/>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" s="2" t="inlineStr">
+      <c r="C370" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4162,8 +3773,7 @@
     <row r="371">
       <c r="A371" t="inlineStr"/>
       <c r="B371" s="2" t="inlineStr"/>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" s="2" t="inlineStr">
+      <c r="C371" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4172,8 +3782,7 @@
     <row r="372">
       <c r="A372" t="inlineStr"/>
       <c r="B372" s="2" t="inlineStr"/>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" s="2" t="inlineStr">
+      <c r="C372" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4182,8 +3791,7 @@
     <row r="373">
       <c r="A373" t="inlineStr"/>
       <c r="B373" s="2" t="inlineStr"/>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" s="2" t="inlineStr">
+      <c r="C373" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4192,8 +3800,7 @@
     <row r="374">
       <c r="A374" t="inlineStr"/>
       <c r="B374" s="2" t="inlineStr"/>
-      <c r="C374" t="inlineStr"/>
-      <c r="D374" s="2" t="inlineStr">
+      <c r="C374" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4202,8 +3809,7 @@
     <row r="375">
       <c r="A375" t="inlineStr"/>
       <c r="B375" s="2" t="inlineStr"/>
-      <c r="C375" t="inlineStr"/>
-      <c r="D375" s="2" t="inlineStr">
+      <c r="C375" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4212,8 +3818,7 @@
     <row r="376">
       <c r="A376" t="inlineStr"/>
       <c r="B376" s="2" t="inlineStr"/>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" s="2" t="inlineStr">
+      <c r="C376" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4222,8 +3827,7 @@
     <row r="377">
       <c r="A377" t="inlineStr"/>
       <c r="B377" s="2" t="inlineStr"/>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" s="2" t="inlineStr">
+      <c r="C377" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4232,8 +3836,7 @@
     <row r="378">
       <c r="A378" t="inlineStr"/>
       <c r="B378" s="2" t="inlineStr"/>
-      <c r="C378" t="inlineStr"/>
-      <c r="D378" s="2" t="inlineStr">
+      <c r="C378" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4242,8 +3845,7 @@
     <row r="379">
       <c r="A379" t="inlineStr"/>
       <c r="B379" s="2" t="inlineStr"/>
-      <c r="C379" t="inlineStr"/>
-      <c r="D379" s="2" t="inlineStr">
+      <c r="C379" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4252,8 +3854,7 @@
     <row r="380">
       <c r="A380" t="inlineStr"/>
       <c r="B380" s="2" t="inlineStr"/>
-      <c r="C380" t="inlineStr"/>
-      <c r="D380" s="2" t="inlineStr">
+      <c r="C380" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4262,8 +3863,7 @@
     <row r="381">
       <c r="A381" t="inlineStr"/>
       <c r="B381" s="2" t="inlineStr"/>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" s="2" t="inlineStr">
+      <c r="C381" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4272,8 +3872,7 @@
     <row r="382">
       <c r="A382" t="inlineStr"/>
       <c r="B382" s="2" t="inlineStr"/>
-      <c r="C382" t="inlineStr"/>
-      <c r="D382" s="2" t="inlineStr">
+      <c r="C382" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4282,8 +3881,7 @@
     <row r="383">
       <c r="A383" t="inlineStr"/>
       <c r="B383" s="2" t="inlineStr"/>
-      <c r="C383" t="inlineStr"/>
-      <c r="D383" s="2" t="inlineStr">
+      <c r="C383" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4292,8 +3890,7 @@
     <row r="384">
       <c r="A384" t="inlineStr"/>
       <c r="B384" s="2" t="inlineStr"/>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" s="2" t="inlineStr">
+      <c r="C384" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4302,8 +3899,7 @@
     <row r="385">
       <c r="A385" t="inlineStr"/>
       <c r="B385" s="2" t="inlineStr"/>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" s="2" t="inlineStr">
+      <c r="C385" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4312,8 +3908,7 @@
     <row r="386">
       <c r="A386" t="inlineStr"/>
       <c r="B386" s="2" t="inlineStr"/>
-      <c r="C386" t="inlineStr"/>
-      <c r="D386" s="2" t="inlineStr">
+      <c r="C386" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4322,8 +3917,7 @@
     <row r="387">
       <c r="A387" t="inlineStr"/>
       <c r="B387" s="2" t="inlineStr"/>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" s="2" t="inlineStr">
+      <c r="C387" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4332,8 +3926,7 @@
     <row r="388">
       <c r="A388" t="inlineStr"/>
       <c r="B388" s="2" t="inlineStr"/>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" s="2" t="inlineStr">
+      <c r="C388" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4342,8 +3935,7 @@
     <row r="389">
       <c r="A389" t="inlineStr"/>
       <c r="B389" s="2" t="inlineStr"/>
-      <c r="C389" t="inlineStr"/>
-      <c r="D389" s="2" t="inlineStr">
+      <c r="C389" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4352,8 +3944,7 @@
     <row r="390">
       <c r="A390" t="inlineStr"/>
       <c r="B390" s="2" t="inlineStr"/>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" s="2" t="inlineStr">
+      <c r="C390" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4362,8 +3953,7 @@
     <row r="391">
       <c r="A391" t="inlineStr"/>
       <c r="B391" s="2" t="inlineStr"/>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" s="2" t="inlineStr">
+      <c r="C391" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4372,8 +3962,7 @@
     <row r="392">
       <c r="A392" t="inlineStr"/>
       <c r="B392" s="2" t="inlineStr"/>
-      <c r="C392" t="inlineStr"/>
-      <c r="D392" s="2" t="inlineStr">
+      <c r="C392" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4382,8 +3971,7 @@
     <row r="393">
       <c r="A393" t="inlineStr"/>
       <c r="B393" s="2" t="inlineStr"/>
-      <c r="C393" t="inlineStr"/>
-      <c r="D393" s="2" t="inlineStr">
+      <c r="C393" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4392,8 +3980,7 @@
     <row r="394">
       <c r="A394" t="inlineStr"/>
       <c r="B394" s="2" t="inlineStr"/>
-      <c r="C394" t="inlineStr"/>
-      <c r="D394" s="2" t="inlineStr">
+      <c r="C394" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4402,8 +3989,7 @@
     <row r="395">
       <c r="A395" t="inlineStr"/>
       <c r="B395" s="2" t="inlineStr"/>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" s="2" t="inlineStr">
+      <c r="C395" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4412,8 +3998,7 @@
     <row r="396">
       <c r="A396" t="inlineStr"/>
       <c r="B396" s="2" t="inlineStr"/>
-      <c r="C396" t="inlineStr"/>
-      <c r="D396" s="2" t="inlineStr">
+      <c r="C396" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4422,8 +4007,7 @@
     <row r="397">
       <c r="A397" t="inlineStr"/>
       <c r="B397" s="2" t="inlineStr"/>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" s="2" t="inlineStr">
+      <c r="C397" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4432,8 +4016,7 @@
     <row r="398">
       <c r="A398" t="inlineStr"/>
       <c r="B398" s="2" t="inlineStr"/>
-      <c r="C398" t="inlineStr"/>
-      <c r="D398" s="2" t="inlineStr">
+      <c r="C398" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4442,8 +4025,7 @@
     <row r="399">
       <c r="A399" t="inlineStr"/>
       <c r="B399" s="2" t="inlineStr"/>
-      <c r="C399" t="inlineStr"/>
-      <c r="D399" s="2" t="inlineStr">
+      <c r="C399" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4452,8 +4034,7 @@
     <row r="400">
       <c r="A400" t="inlineStr"/>
       <c r="B400" s="2" t="inlineStr"/>
-      <c r="C400" t="inlineStr"/>
-      <c r="D400" s="2" t="inlineStr">
+      <c r="C400" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4462,8 +4043,7 @@
     <row r="401">
       <c r="A401" t="inlineStr"/>
       <c r="B401" s="2" t="inlineStr"/>
-      <c r="C401" t="inlineStr"/>
-      <c r="D401" s="2" t="inlineStr">
+      <c r="C401" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4472,8 +4052,7 @@
     <row r="402">
       <c r="A402" t="inlineStr"/>
       <c r="B402" s="2" t="inlineStr"/>
-      <c r="C402" t="inlineStr"/>
-      <c r="D402" s="2" t="inlineStr">
+      <c r="C402" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4482,8 +4061,7 @@
     <row r="403">
       <c r="A403" t="inlineStr"/>
       <c r="B403" s="2" t="inlineStr"/>
-      <c r="C403" t="inlineStr"/>
-      <c r="D403" s="2" t="inlineStr">
+      <c r="C403" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4492,8 +4070,7 @@
     <row r="404">
       <c r="A404" t="inlineStr"/>
       <c r="B404" s="2" t="inlineStr"/>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" s="2" t="inlineStr">
+      <c r="C404" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4502,8 +4079,7 @@
     <row r="405">
       <c r="A405" t="inlineStr"/>
       <c r="B405" s="2" t="inlineStr"/>
-      <c r="C405" t="inlineStr"/>
-      <c r="D405" s="2" t="inlineStr">
+      <c r="C405" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4512,8 +4088,7 @@
     <row r="406">
       <c r="A406" t="inlineStr"/>
       <c r="B406" s="2" t="inlineStr"/>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" s="2" t="inlineStr">
+      <c r="C406" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4522,8 +4097,7 @@
     <row r="407">
       <c r="A407" t="inlineStr"/>
       <c r="B407" s="2" t="inlineStr"/>
-      <c r="C407" t="inlineStr"/>
-      <c r="D407" s="2" t="inlineStr">
+      <c r="C407" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4532,8 +4106,7 @@
     <row r="408">
       <c r="A408" t="inlineStr"/>
       <c r="B408" s="2" t="inlineStr"/>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" s="2" t="inlineStr">
+      <c r="C408" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4542,8 +4115,7 @@
     <row r="409">
       <c r="A409" t="inlineStr"/>
       <c r="B409" s="2" t="inlineStr"/>
-      <c r="C409" t="inlineStr"/>
-      <c r="D409" s="2" t="inlineStr">
+      <c r="C409" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4552,8 +4124,7 @@
     <row r="410">
       <c r="A410" t="inlineStr"/>
       <c r="B410" s="2" t="inlineStr"/>
-      <c r="C410" t="inlineStr"/>
-      <c r="D410" s="2" t="inlineStr">
+      <c r="C410" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4562,8 +4133,7 @@
     <row r="411">
       <c r="A411" t="inlineStr"/>
       <c r="B411" s="2" t="inlineStr"/>
-      <c r="C411" t="inlineStr"/>
-      <c r="D411" s="2" t="inlineStr">
+      <c r="C411" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4572,8 +4142,7 @@
     <row r="412">
       <c r="A412" t="inlineStr"/>
       <c r="B412" s="2" t="inlineStr"/>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" s="2" t="inlineStr">
+      <c r="C412" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4582,8 +4151,7 @@
     <row r="413">
       <c r="A413" t="inlineStr"/>
       <c r="B413" s="2" t="inlineStr"/>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" s="2" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4592,8 +4160,7 @@
     <row r="414">
       <c r="A414" t="inlineStr"/>
       <c r="B414" s="2" t="inlineStr"/>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" s="2" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4602,8 +4169,7 @@
     <row r="415">
       <c r="A415" t="inlineStr"/>
       <c r="B415" s="2" t="inlineStr"/>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" s="2" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4612,8 +4178,7 @@
     <row r="416">
       <c r="A416" t="inlineStr"/>
       <c r="B416" s="2" t="inlineStr"/>
-      <c r="C416" t="inlineStr"/>
-      <c r="D416" s="2" t="inlineStr">
+      <c r="C416" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4622,8 +4187,7 @@
     <row r="417">
       <c r="A417" t="inlineStr"/>
       <c r="B417" s="2" t="inlineStr"/>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" s="2" t="inlineStr">
+      <c r="C417" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4632,8 +4196,7 @@
     <row r="418">
       <c r="A418" t="inlineStr"/>
       <c r="B418" s="2" t="inlineStr"/>
-      <c r="C418" t="inlineStr"/>
-      <c r="D418" s="2" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4642,8 +4205,7 @@
     <row r="419">
       <c r="A419" t="inlineStr"/>
       <c r="B419" s="2" t="inlineStr"/>
-      <c r="C419" t="inlineStr"/>
-      <c r="D419" s="2" t="inlineStr">
+      <c r="C419" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4652,8 +4214,7 @@
     <row r="420">
       <c r="A420" t="inlineStr"/>
       <c r="B420" s="2" t="inlineStr"/>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" s="2" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4662,8 +4223,7 @@
     <row r="421">
       <c r="A421" t="inlineStr"/>
       <c r="B421" s="2" t="inlineStr"/>
-      <c r="C421" t="inlineStr"/>
-      <c r="D421" s="2" t="inlineStr">
+      <c r="C421" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4672,8 +4232,7 @@
     <row r="422">
       <c r="A422" t="inlineStr"/>
       <c r="B422" s="2" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
-      <c r="D422" s="2" t="inlineStr">
+      <c r="C422" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4682,8 +4241,7 @@
     <row r="423">
       <c r="A423" t="inlineStr"/>
       <c r="B423" s="2" t="inlineStr"/>
-      <c r="C423" t="inlineStr"/>
-      <c r="D423" s="2" t="inlineStr">
+      <c r="C423" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4692,8 +4250,7 @@
     <row r="424">
       <c r="A424" t="inlineStr"/>
       <c r="B424" s="2" t="inlineStr"/>
-      <c r="C424" t="inlineStr"/>
-      <c r="D424" s="2" t="inlineStr">
+      <c r="C424" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4702,8 +4259,7 @@
     <row r="425">
       <c r="A425" t="inlineStr"/>
       <c r="B425" s="2" t="inlineStr"/>
-      <c r="C425" t="inlineStr"/>
-      <c r="D425" s="2" t="inlineStr">
+      <c r="C425" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4712,8 +4268,7 @@
     <row r="426">
       <c r="A426" t="inlineStr"/>
       <c r="B426" s="2" t="inlineStr"/>
-      <c r="C426" t="inlineStr"/>
-      <c r="D426" s="2" t="inlineStr">
+      <c r="C426" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4722,8 +4277,7 @@
     <row r="427">
       <c r="A427" t="inlineStr"/>
       <c r="B427" s="2" t="inlineStr"/>
-      <c r="C427" t="inlineStr"/>
-      <c r="D427" s="2" t="inlineStr">
+      <c r="C427" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4732,8 +4286,7 @@
     <row r="428">
       <c r="A428" t="inlineStr"/>
       <c r="B428" s="2" t="inlineStr"/>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" s="2" t="inlineStr">
+      <c r="C428" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4742,8 +4295,7 @@
     <row r="429">
       <c r="A429" t="inlineStr"/>
       <c r="B429" s="2" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
-      <c r="D429" s="2" t="inlineStr">
+      <c r="C429" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4752,8 +4304,7 @@
     <row r="430">
       <c r="A430" t="inlineStr"/>
       <c r="B430" s="2" t="inlineStr"/>
-      <c r="C430" t="inlineStr"/>
-      <c r="D430" s="2" t="inlineStr">
+      <c r="C430" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4762,8 +4313,7 @@
     <row r="431">
       <c r="A431" t="inlineStr"/>
       <c r="B431" s="2" t="inlineStr"/>
-      <c r="C431" t="inlineStr"/>
-      <c r="D431" s="2" t="inlineStr">
+      <c r="C431" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4772,8 +4322,7 @@
     <row r="432">
       <c r="A432" t="inlineStr"/>
       <c r="B432" s="2" t="inlineStr"/>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" s="2" t="inlineStr">
+      <c r="C432" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4782,8 +4331,7 @@
     <row r="433">
       <c r="A433" t="inlineStr"/>
       <c r="B433" s="2" t="inlineStr"/>
-      <c r="C433" t="inlineStr"/>
-      <c r="D433" s="2" t="inlineStr">
+      <c r="C433" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4792,8 +4340,7 @@
     <row r="434">
       <c r="A434" t="inlineStr"/>
       <c r="B434" s="2" t="inlineStr"/>
-      <c r="C434" t="inlineStr"/>
-      <c r="D434" s="2" t="inlineStr">
+      <c r="C434" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4802,8 +4349,7 @@
     <row r="435">
       <c r="A435" t="inlineStr"/>
       <c r="B435" s="2" t="inlineStr"/>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" s="2" t="inlineStr">
+      <c r="C435" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4812,8 +4358,7 @@
     <row r="436">
       <c r="A436" t="inlineStr"/>
       <c r="B436" s="2" t="inlineStr"/>
-      <c r="C436" t="inlineStr"/>
-      <c r="D436" s="2" t="inlineStr">
+      <c r="C436" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4822,8 +4367,7 @@
     <row r="437">
       <c r="A437" t="inlineStr"/>
       <c r="B437" s="2" t="inlineStr"/>
-      <c r="C437" t="inlineStr"/>
-      <c r="D437" s="2" t="inlineStr">
+      <c r="C437" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4832,8 +4376,7 @@
     <row r="438">
       <c r="A438" t="inlineStr"/>
       <c r="B438" s="2" t="inlineStr"/>
-      <c r="C438" t="inlineStr"/>
-      <c r="D438" s="2" t="inlineStr">
+      <c r="C438" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4842,8 +4385,7 @@
     <row r="439">
       <c r="A439" t="inlineStr"/>
       <c r="B439" s="2" t="inlineStr"/>
-      <c r="C439" t="inlineStr"/>
-      <c r="D439" s="2" t="inlineStr">
+      <c r="C439" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4852,8 +4394,7 @@
     <row r="440">
       <c r="A440" t="inlineStr"/>
       <c r="B440" s="2" t="inlineStr"/>
-      <c r="C440" t="inlineStr"/>
-      <c r="D440" s="2" t="inlineStr">
+      <c r="C440" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4862,8 +4403,7 @@
     <row r="441">
       <c r="A441" t="inlineStr"/>
       <c r="B441" s="2" t="inlineStr"/>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" s="2" t="inlineStr">
+      <c r="C441" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4872,8 +4412,7 @@
     <row r="442">
       <c r="A442" t="inlineStr"/>
       <c r="B442" s="2" t="inlineStr"/>
-      <c r="C442" t="inlineStr"/>
-      <c r="D442" s="2" t="inlineStr">
+      <c r="C442" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4882,8 +4421,7 @@
     <row r="443">
       <c r="A443" t="inlineStr"/>
       <c r="B443" s="2" t="inlineStr"/>
-      <c r="C443" t="inlineStr"/>
-      <c r="D443" s="2" t="inlineStr">
+      <c r="C443" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4892,8 +4430,7 @@
     <row r="444">
       <c r="A444" t="inlineStr"/>
       <c r="B444" s="2" t="inlineStr"/>
-      <c r="C444" t="inlineStr"/>
-      <c r="D444" s="2" t="inlineStr">
+      <c r="C444" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4902,8 +4439,7 @@
     <row r="445">
       <c r="A445" t="inlineStr"/>
       <c r="B445" s="2" t="inlineStr"/>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" s="2" t="inlineStr">
+      <c r="C445" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4912,8 +4448,7 @@
     <row r="446">
       <c r="A446" t="inlineStr"/>
       <c r="B446" s="2" t="inlineStr"/>
-      <c r="C446" t="inlineStr"/>
-      <c r="D446" s="2" t="inlineStr">
+      <c r="C446" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4922,8 +4457,7 @@
     <row r="447">
       <c r="A447" t="inlineStr"/>
       <c r="B447" s="2" t="inlineStr"/>
-      <c r="C447" t="inlineStr"/>
-      <c r="D447" s="2" t="inlineStr">
+      <c r="C447" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4932,8 +4466,7 @@
     <row r="448">
       <c r="A448" t="inlineStr"/>
       <c r="B448" s="2" t="inlineStr"/>
-      <c r="C448" t="inlineStr"/>
-      <c r="D448" s="2" t="inlineStr">
+      <c r="C448" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4942,8 +4475,7 @@
     <row r="449">
       <c r="A449" t="inlineStr"/>
       <c r="B449" s="2" t="inlineStr"/>
-      <c r="C449" t="inlineStr"/>
-      <c r="D449" s="2" t="inlineStr">
+      <c r="C449" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4952,8 +4484,7 @@
     <row r="450">
       <c r="A450" t="inlineStr"/>
       <c r="B450" s="2" t="inlineStr"/>
-      <c r="C450" t="inlineStr"/>
-      <c r="D450" s="2" t="inlineStr">
+      <c r="C450" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4962,8 +4493,7 @@
     <row r="451">
       <c r="A451" t="inlineStr"/>
       <c r="B451" s="2" t="inlineStr"/>
-      <c r="C451" t="inlineStr"/>
-      <c r="D451" s="2" t="inlineStr">
+      <c r="C451" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4972,8 +4502,7 @@
     <row r="452">
       <c r="A452" t="inlineStr"/>
       <c r="B452" s="2" t="inlineStr"/>
-      <c r="C452" t="inlineStr"/>
-      <c r="D452" s="2" t="inlineStr">
+      <c r="C452" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4982,8 +4511,7 @@
     <row r="453">
       <c r="A453" t="inlineStr"/>
       <c r="B453" s="2" t="inlineStr"/>
-      <c r="C453" t="inlineStr"/>
-      <c r="D453" s="2" t="inlineStr">
+      <c r="C453" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -4992,8 +4520,7 @@
     <row r="454">
       <c r="A454" t="inlineStr"/>
       <c r="B454" s="2" t="inlineStr"/>
-      <c r="C454" t="inlineStr"/>
-      <c r="D454" s="2" t="inlineStr">
+      <c r="C454" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5002,8 +4529,7 @@
     <row r="455">
       <c r="A455" t="inlineStr"/>
       <c r="B455" s="2" t="inlineStr"/>
-      <c r="C455" t="inlineStr"/>
-      <c r="D455" s="2" t="inlineStr">
+      <c r="C455" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5012,8 +4538,7 @@
     <row r="456">
       <c r="A456" t="inlineStr"/>
       <c r="B456" s="2" t="inlineStr"/>
-      <c r="C456" t="inlineStr"/>
-      <c r="D456" s="2" t="inlineStr">
+      <c r="C456" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5022,8 +4547,7 @@
     <row r="457">
       <c r="A457" t="inlineStr"/>
       <c r="B457" s="2" t="inlineStr"/>
-      <c r="C457" t="inlineStr"/>
-      <c r="D457" s="2" t="inlineStr">
+      <c r="C457" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5032,8 +4556,7 @@
     <row r="458">
       <c r="A458" t="inlineStr"/>
       <c r="B458" s="2" t="inlineStr"/>
-      <c r="C458" t="inlineStr"/>
-      <c r="D458" s="2" t="inlineStr">
+      <c r="C458" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5042,8 +4565,7 @@
     <row r="459">
       <c r="A459" t="inlineStr"/>
       <c r="B459" s="2" t="inlineStr"/>
-      <c r="C459" t="inlineStr"/>
-      <c r="D459" s="2" t="inlineStr">
+      <c r="C459" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5052,8 +4574,7 @@
     <row r="460">
       <c r="A460" t="inlineStr"/>
       <c r="B460" s="2" t="inlineStr"/>
-      <c r="C460" t="inlineStr"/>
-      <c r="D460" s="2" t="inlineStr">
+      <c r="C460" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5062,8 +4583,7 @@
     <row r="461">
       <c r="A461" t="inlineStr"/>
       <c r="B461" s="2" t="inlineStr"/>
-      <c r="C461" t="inlineStr"/>
-      <c r="D461" s="2" t="inlineStr">
+      <c r="C461" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5072,8 +4592,7 @@
     <row r="462">
       <c r="A462" t="inlineStr"/>
       <c r="B462" s="2" t="inlineStr"/>
-      <c r="C462" t="inlineStr"/>
-      <c r="D462" s="2" t="inlineStr">
+      <c r="C462" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5082,8 +4601,7 @@
     <row r="463">
       <c r="A463" t="inlineStr"/>
       <c r="B463" s="2" t="inlineStr"/>
-      <c r="C463" t="inlineStr"/>
-      <c r="D463" s="2" t="inlineStr">
+      <c r="C463" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5092,8 +4610,7 @@
     <row r="464">
       <c r="A464" t="inlineStr"/>
       <c r="B464" s="2" t="inlineStr"/>
-      <c r="C464" t="inlineStr"/>
-      <c r="D464" s="2" t="inlineStr">
+      <c r="C464" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5102,8 +4619,7 @@
     <row r="465">
       <c r="A465" t="inlineStr"/>
       <c r="B465" s="2" t="inlineStr"/>
-      <c r="C465" t="inlineStr"/>
-      <c r="D465" s="2" t="inlineStr">
+      <c r="C465" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5112,8 +4628,7 @@
     <row r="466">
       <c r="A466" t="inlineStr"/>
       <c r="B466" s="2" t="inlineStr"/>
-      <c r="C466" t="inlineStr"/>
-      <c r="D466" s="2" t="inlineStr">
+      <c r="C466" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5122,8 +4637,7 @@
     <row r="467">
       <c r="A467" t="inlineStr"/>
       <c r="B467" s="2" t="inlineStr"/>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" s="2" t="inlineStr">
+      <c r="C467" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5132,8 +4646,7 @@
     <row r="468">
       <c r="A468" t="inlineStr"/>
       <c r="B468" s="2" t="inlineStr"/>
-      <c r="C468" t="inlineStr"/>
-      <c r="D468" s="2" t="inlineStr">
+      <c r="C468" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5142,8 +4655,7 @@
     <row r="469">
       <c r="A469" t="inlineStr"/>
       <c r="B469" s="2" t="inlineStr"/>
-      <c r="C469" t="inlineStr"/>
-      <c r="D469" s="2" t="inlineStr">
+      <c r="C469" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5152,8 +4664,7 @@
     <row r="470">
       <c r="A470" t="inlineStr"/>
       <c r="B470" s="2" t="inlineStr"/>
-      <c r="C470" t="inlineStr"/>
-      <c r="D470" s="2" t="inlineStr">
+      <c r="C470" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5162,8 +4673,7 @@
     <row r="471">
       <c r="A471" t="inlineStr"/>
       <c r="B471" s="2" t="inlineStr"/>
-      <c r="C471" t="inlineStr"/>
-      <c r="D471" s="2" t="inlineStr">
+      <c r="C471" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5172,8 +4682,7 @@
     <row r="472">
       <c r="A472" t="inlineStr"/>
       <c r="B472" s="2" t="inlineStr"/>
-      <c r="C472" t="inlineStr"/>
-      <c r="D472" s="2" t="inlineStr">
+      <c r="C472" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5182,8 +4691,7 @@
     <row r="473">
       <c r="A473" t="inlineStr"/>
       <c r="B473" s="2" t="inlineStr"/>
-      <c r="C473" t="inlineStr"/>
-      <c r="D473" s="2" t="inlineStr">
+      <c r="C473" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5192,8 +4700,7 @@
     <row r="474">
       <c r="A474" t="inlineStr"/>
       <c r="B474" s="2" t="inlineStr"/>
-      <c r="C474" t="inlineStr"/>
-      <c r="D474" s="2" t="inlineStr">
+      <c r="C474" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5202,8 +4709,7 @@
     <row r="475">
       <c r="A475" t="inlineStr"/>
       <c r="B475" s="2" t="inlineStr"/>
-      <c r="C475" t="inlineStr"/>
-      <c r="D475" s="2" t="inlineStr">
+      <c r="C475" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5212,8 +4718,7 @@
     <row r="476">
       <c r="A476" t="inlineStr"/>
       <c r="B476" s="2" t="inlineStr"/>
-      <c r="C476" t="inlineStr"/>
-      <c r="D476" s="2" t="inlineStr">
+      <c r="C476" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5222,8 +4727,7 @@
     <row r="477">
       <c r="A477" t="inlineStr"/>
       <c r="B477" s="2" t="inlineStr"/>
-      <c r="C477" t="inlineStr"/>
-      <c r="D477" s="2" t="inlineStr">
+      <c r="C477" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5232,8 +4736,7 @@
     <row r="478">
       <c r="A478" t="inlineStr"/>
       <c r="B478" s="2" t="inlineStr"/>
-      <c r="C478" t="inlineStr"/>
-      <c r="D478" s="2" t="inlineStr">
+      <c r="C478" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5242,8 +4745,7 @@
     <row r="479">
       <c r="A479" t="inlineStr"/>
       <c r="B479" s="2" t="inlineStr"/>
-      <c r="C479" t="inlineStr"/>
-      <c r="D479" s="2" t="inlineStr">
+      <c r="C479" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5252,8 +4754,7 @@
     <row r="480">
       <c r="A480" t="inlineStr"/>
       <c r="B480" s="2" t="inlineStr"/>
-      <c r="C480" t="inlineStr"/>
-      <c r="D480" s="2" t="inlineStr">
+      <c r="C480" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5262,8 +4763,7 @@
     <row r="481">
       <c r="A481" t="inlineStr"/>
       <c r="B481" s="2" t="inlineStr"/>
-      <c r="C481" t="inlineStr"/>
-      <c r="D481" s="2" t="inlineStr">
+      <c r="C481" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5272,8 +4772,7 @@
     <row r="482">
       <c r="A482" t="inlineStr"/>
       <c r="B482" s="2" t="inlineStr"/>
-      <c r="C482" t="inlineStr"/>
-      <c r="D482" s="2" t="inlineStr">
+      <c r="C482" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5282,8 +4781,7 @@
     <row r="483">
       <c r="A483" t="inlineStr"/>
       <c r="B483" s="2" t="inlineStr"/>
-      <c r="C483" t="inlineStr"/>
-      <c r="D483" s="2" t="inlineStr">
+      <c r="C483" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5292,8 +4790,7 @@
     <row r="484">
       <c r="A484" t="inlineStr"/>
       <c r="B484" s="2" t="inlineStr"/>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" s="2" t="inlineStr">
+      <c r="C484" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5302,8 +4799,7 @@
     <row r="485">
       <c r="A485" t="inlineStr"/>
       <c r="B485" s="2" t="inlineStr"/>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" s="2" t="inlineStr">
+      <c r="C485" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5312,8 +4808,7 @@
     <row r="486">
       <c r="A486" t="inlineStr"/>
       <c r="B486" s="2" t="inlineStr"/>
-      <c r="C486" t="inlineStr"/>
-      <c r="D486" s="2" t="inlineStr">
+      <c r="C486" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5322,8 +4817,7 @@
     <row r="487">
       <c r="A487" t="inlineStr"/>
       <c r="B487" s="2" t="inlineStr"/>
-      <c r="C487" t="inlineStr"/>
-      <c r="D487" s="2" t="inlineStr">
+      <c r="C487" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5332,8 +4826,7 @@
     <row r="488">
       <c r="A488" t="inlineStr"/>
       <c r="B488" s="2" t="inlineStr"/>
-      <c r="C488" t="inlineStr"/>
-      <c r="D488" s="2" t="inlineStr">
+      <c r="C488" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5342,8 +4835,7 @@
     <row r="489">
       <c r="A489" t="inlineStr"/>
       <c r="B489" s="2" t="inlineStr"/>
-      <c r="C489" t="inlineStr"/>
-      <c r="D489" s="2" t="inlineStr">
+      <c r="C489" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5352,8 +4844,7 @@
     <row r="490">
       <c r="A490" t="inlineStr"/>
       <c r="B490" s="2" t="inlineStr"/>
-      <c r="C490" t="inlineStr"/>
-      <c r="D490" s="2" t="inlineStr">
+      <c r="C490" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5362,8 +4853,7 @@
     <row r="491">
       <c r="A491" t="inlineStr"/>
       <c r="B491" s="2" t="inlineStr"/>
-      <c r="C491" t="inlineStr"/>
-      <c r="D491" s="2" t="inlineStr">
+      <c r="C491" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5372,8 +4862,7 @@
     <row r="492">
       <c r="A492" t="inlineStr"/>
       <c r="B492" s="2" t="inlineStr"/>
-      <c r="C492" t="inlineStr"/>
-      <c r="D492" s="2" t="inlineStr">
+      <c r="C492" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5382,8 +4871,7 @@
     <row r="493">
       <c r="A493" t="inlineStr"/>
       <c r="B493" s="2" t="inlineStr"/>
-      <c r="C493" t="inlineStr"/>
-      <c r="D493" s="2" t="inlineStr">
+      <c r="C493" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5392,8 +4880,7 @@
     <row r="494">
       <c r="A494" t="inlineStr"/>
       <c r="B494" s="2" t="inlineStr"/>
-      <c r="C494" t="inlineStr"/>
-      <c r="D494" s="2" t="inlineStr">
+      <c r="C494" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5402,8 +4889,7 @@
     <row r="495">
       <c r="A495" t="inlineStr"/>
       <c r="B495" s="2" t="inlineStr"/>
-      <c r="C495" t="inlineStr"/>
-      <c r="D495" s="2" t="inlineStr">
+      <c r="C495" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5412,8 +4898,7 @@
     <row r="496">
       <c r="A496" t="inlineStr"/>
       <c r="B496" s="2" t="inlineStr"/>
-      <c r="C496" t="inlineStr"/>
-      <c r="D496" s="2" t="inlineStr">
+      <c r="C496" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5422,8 +4907,7 @@
     <row r="497">
       <c r="A497" t="inlineStr"/>
       <c r="B497" s="2" t="inlineStr"/>
-      <c r="C497" t="inlineStr"/>
-      <c r="D497" s="2" t="inlineStr">
+      <c r="C497" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5432,8 +4916,7 @@
     <row r="498">
       <c r="A498" t="inlineStr"/>
       <c r="B498" s="2" t="inlineStr"/>
-      <c r="C498" t="inlineStr"/>
-      <c r="D498" s="2" t="inlineStr">
+      <c r="C498" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5442,8 +4925,7 @@
     <row r="499">
       <c r="A499" t="inlineStr"/>
       <c r="B499" s="2" t="inlineStr"/>
-      <c r="C499" t="inlineStr"/>
-      <c r="D499" s="2" t="inlineStr">
+      <c r="C499" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5452,8 +4934,7 @@
     <row r="500">
       <c r="A500" t="inlineStr"/>
       <c r="B500" s="2" t="inlineStr"/>
-      <c r="C500" t="inlineStr"/>
-      <c r="D500" s="2" t="inlineStr">
+      <c r="C500" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
@@ -5462,20 +4943,14 @@
     <row r="501">
       <c r="A501" t="inlineStr"/>
       <c r="B501" s="2" t="inlineStr"/>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" s="2" t="inlineStr">
+      <c r="C501" t="inlineStr">
         <is>
           <t>Sagar Kothakula</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D501"/>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Male,Female"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:C501"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5486,11 +4961,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5499,98 +4974,99 @@
           <t>Abra Zylo Customer Import Template</t>
         </is>
       </c>
+      <c r="B1" s="3" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>How to use</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fill the Customers sheet, then upload this same file in Abra Zylo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fill these columns in the Customers sheet:</t>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Required. Enter the customer full name.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Mobile Number</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Customer full name</t>
+          <t>Required. Enter a 10-digit Indian mobile number starting with 6, 7, 8 or 9.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mobile Number</t>
+          <t>Security Code</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10-digit Indian mobile number starting with 6, 7, 8 or 9</t>
+          <t>Do not change it. Every customer row must contain exactly: Sagar Kothakula</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Blank rows</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Male or Female</t>
+          <t>You may leave unused rows blank. The prefilled Security Code on unused template rows is ignored.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Security Code</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Must remain exactly: Sagar Kothakula</t>
+          <t>If a populated customer row has a missing or different Security Code, the entire upload is rejected.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Duplicates</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Existing/duplicate mobile numbers are skipped and are not created again.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Do not rename the column headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Do not change the Security Code.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Only populated customer rows are imported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+          <t>Limit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Maximum 500 customer rows per upload.</t>
         </is>
